--- a/Supplementary Table.xlsx
+++ b/Supplementary Table.xlsx
@@ -1,21 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MATLAB Drive\0 Mis-used Ratios\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49AB27D1-2B66-417C-A445-569D80873BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B479BB-B9BA-4420-BD6F-453337800ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -182,13 +193,13 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -530,16 +541,16 @@
       <c r="A1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
       <c r="G1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
       <c r="J1" s="2" t="s">
         <v>28</v>
       </c>
@@ -548,8 +559,8 @@
       <c r="M1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
       <c r="P1" s="2" t="s">
         <v>31</v>
       </c>
@@ -558,18 +569,18 @@
       <c r="S1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
       <c r="V1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
       <c r="Y1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -716,7 +727,7 @@
         <v>1254.7900036484957</v>
       </c>
       <c r="U3">
-        <v>146</v>
+        <v>1460</v>
       </c>
       <c r="V3">
         <v>83.183183183183189</v>
@@ -799,7 +810,7 @@
         <v>1218.4587819039689</v>
       </c>
       <c r="U4">
-        <v>150</v>
+        <v>1500</v>
       </c>
       <c r="V4">
         <v>85.285285285285283</v>
@@ -882,7 +893,7 @@
         <v>1185.3007677572375</v>
       </c>
       <c r="U5">
-        <v>154</v>
+        <v>1540</v>
       </c>
       <c r="V5">
         <v>86.486486486486484</v>
@@ -965,7 +976,7 @@
         <v>1155.0744136527319</v>
       </c>
       <c r="U6">
-        <v>143</v>
+        <v>1430</v>
       </c>
       <c r="V6">
         <v>87.687687687687685</v>
@@ -1048,7 +1059,7 @@
         <v>1127.2100222077506</v>
       </c>
       <c r="U7">
-        <v>137</v>
+        <v>1370</v>
       </c>
       <c r="V7">
         <v>88.288288288288285</v>
@@ -1131,7 +1142,7 @@
         <v>1101.3479156220656</v>
       </c>
       <c r="U8">
-        <v>134</v>
+        <v>1340</v>
       </c>
       <c r="V8">
         <v>88.588588588588593</v>
@@ -1214,7 +1225,7 @@
         <v>1077.4441901389296</v>
       </c>
       <c r="U9">
-        <v>130</v>
+        <v>1300</v>
       </c>
       <c r="V9">
         <v>89.189189189189193</v>
@@ -1297,7 +1308,7 @@
         <v>1055.3565447252481</v>
       </c>
       <c r="U10">
-        <v>124</v>
+        <v>1240</v>
       </c>
       <c r="V10">
         <v>89.489489489489486</v>
@@ -1380,7 +1391,7 @@
         <v>1185.3007677572375</v>
       </c>
       <c r="U11">
-        <v>141</v>
+        <v>1410</v>
       </c>
       <c r="V11">
         <v>86.486486486486484</v>
@@ -1463,7 +1474,7 @@
         <v>1097.9696909347431</v>
       </c>
       <c r="U12">
-        <v>134</v>
+        <v>1340</v>
       </c>
       <c r="V12">
         <v>95.195195195195197</v>
@@ -1546,7 +1557,7 @@
         <v>1023.7740192931205</v>
       </c>
       <c r="U13">
-        <v>116</v>
+        <v>1160</v>
       </c>
       <c r="V13">
         <v>103.003003003003</v>
@@ -1629,7 +1640,7 @@
         <v>959.83444486561802</v>
       </c>
       <c r="U14">
-        <v>121</v>
+        <v>1210</v>
       </c>
       <c r="V14">
         <v>109.90990990990991</v>
@@ -1712,7 +1723,7 @@
         <v>904.21083189031901</v>
       </c>
       <c r="U15">
-        <v>117</v>
+        <v>1170</v>
       </c>
       <c r="V15">
         <v>115.91591591591592</v>
@@ -1795,7 +1806,7 @@
         <v>855.30915700348783</v>
       </c>
       <c r="U16">
-        <v>108</v>
+        <v>1080</v>
       </c>
       <c r="V16">
         <v>121.62162162162163</v>
@@ -1878,7 +1889,7 @@
         <v>811.58397576218056</v>
       </c>
       <c r="U17">
-        <v>101</v>
+        <v>1010</v>
       </c>
       <c r="V17">
         <v>126.72672672672672</v>
@@ -1961,7 +1972,7 @@
         <v>772.69221839295528</v>
       </c>
       <c r="U18">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="V18">
         <v>130.93093093093094</v>
@@ -2044,7 +2055,7 @@
         <v>48.877950909753785</v>
       </c>
       <c r="U19">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="V19">
         <v>0</v>
@@ -2127,7 +2138,7 @@
         <v>277.93642829643551</v>
       </c>
       <c r="U20">
-        <v>42</v>
+        <v>420</v>
       </c>
       <c r="V20">
         <v>147.14714714714714</v>
@@ -2210,7 +2221,7 @@
         <v>587.75222342041138</v>
       </c>
       <c r="U21">
-        <v>76</v>
+        <v>760</v>
       </c>
       <c r="V21">
         <v>112.61261261261261</v>
@@ -2293,7 +2304,7 @@
         <v>900.24854698246554</v>
       </c>
       <c r="U22">
-        <v>108</v>
+        <v>1080</v>
       </c>
       <c r="V22">
         <v>96.09609609609609</v>
@@ -2376,7 +2387,7 @@
         <v>1185.3007677572375</v>
       </c>
       <c r="U23">
-        <v>142</v>
+        <v>1420</v>
       </c>
       <c r="V23">
         <v>86.486486486486484</v>
@@ -2459,7 +2470,7 @@
         <v>1435.8753518343201</v>
       </c>
       <c r="U24">
-        <v>170</v>
+        <v>1700</v>
       </c>
       <c r="V24">
         <v>80.48048048048048</v>
@@ -2542,7 +2553,7 @@
         <v>1653.2631561637011</v>
       </c>
       <c r="U25">
-        <v>188</v>
+        <v>1880</v>
       </c>
       <c r="V25">
         <v>75.97597597597597</v>
@@ -2625,7 +2636,7 @@
         <v>1840.9912813957571</v>
       </c>
       <c r="U26">
-        <v>206</v>
+        <v>2060</v>
       </c>
       <c r="V26">
         <v>72.672672672672675</v>
@@ -2708,7 +2719,7 @@
         <v>1185.3007677572375</v>
       </c>
       <c r="U27">
-        <v>142</v>
+        <v>1420</v>
       </c>
       <c r="V27">
         <v>86.486486486486484</v>
@@ -2791,7 +2802,7 @@
         <v>1271.7820936946562</v>
       </c>
       <c r="U28">
-        <v>146</v>
+        <v>1460</v>
       </c>
       <c r="V28">
         <v>79.27927927927928</v>
@@ -2874,7 +2885,7 @@
         <v>1351.1696831373774</v>
       </c>
       <c r="U29">
-        <v>165</v>
+        <v>1650</v>
       </c>
       <c r="V29">
         <v>75.37537537537537</v>
@@ -2957,7 +2968,7 @@
         <v>1424.4254563350371</v>
       </c>
       <c r="U30">
-        <v>170</v>
+        <v>1700</v>
       </c>
       <c r="V30">
         <v>72.972972972972968</v>
@@ -3040,7 +3051,7 @@
         <v>1491.2497265990514</v>
       </c>
       <c r="U31">
-        <v>172</v>
+        <v>1720</v>
       </c>
       <c r="V31">
         <v>71.171171171171167</v>
@@ -3123,7 +3134,7 @@
         <v>1551.5867218435021</v>
       </c>
       <c r="U32">
-        <v>173</v>
+        <v>1730</v>
       </c>
       <c r="V32">
         <v>69.969969969969966</v>
@@ -3206,7 +3217,7 @@
         <v>1606.3806479168438</v>
       </c>
       <c r="U33">
-        <v>187</v>
+        <v>1870</v>
       </c>
       <c r="V33">
         <v>69.069069069069073</v>
@@ -3289,7 +3300,7 @@
         <v>1656.2225701641437</v>
       </c>
       <c r="U34">
-        <v>198</v>
+        <v>1980</v>
       </c>
       <c r="V34">
         <v>68.468468468468473</v>
@@ -3372,7 +3383,7 @@
         <v>1347.8742177590516</v>
       </c>
       <c r="U35">
-        <v>159</v>
+        <v>1590</v>
       </c>
       <c r="V35">
         <v>82.582582582582589</v>
@@ -3455,7 +3466,7 @@
         <v>1266.1195020353043</v>
       </c>
       <c r="U36">
-        <v>159</v>
+        <v>1590</v>
       </c>
       <c r="V36">
         <v>84.38438438438439</v>
@@ -3538,7 +3549,7 @@
         <v>1185.3007677572382</v>
       </c>
       <c r="U37">
-        <v>147</v>
+        <v>1470</v>
       </c>
       <c r="V37">
         <v>86.486486486486484</v>
@@ -3621,7 +3632,7 @@
         <v>1105.6391762616065</v>
       </c>
       <c r="U38">
-        <v>130</v>
+        <v>1300</v>
       </c>
       <c r="V38">
         <v>89.189189189189193</v>
@@ -3704,7 +3715,7 @@
         <v>1026.918957136648</v>
       </c>
       <c r="U39">
-        <v>130</v>
+        <v>1300</v>
       </c>
       <c r="V39">
         <v>91.891891891891888</v>
@@ -3787,7 +3798,7 @@
         <v>949.22695800805718</v>
       </c>
       <c r="U40">
-        <v>124</v>
+        <v>1240</v>
       </c>
       <c r="V40">
         <v>94.89489489489489</v>
@@ -3870,7 +3881,7 @@
         <v>872.79463828719804</v>
       </c>
       <c r="U41">
-        <v>112</v>
+        <v>1120</v>
       </c>
       <c r="V41">
         <v>98.198198198198199</v>
@@ -3953,7 +3964,7 @@
         <v>797.80588821415336</v>
       </c>
       <c r="U42">
-        <v>110</v>
+        <v>1100</v>
       </c>
       <c r="V42">
         <v>102.10210210210211</v>
@@ -4036,7 +4047,7 @@
         <v>140.87990788070775</v>
       </c>
       <c r="U43">
-        <v>33</v>
+        <v>330</v>
       </c>
       <c r="V43">
         <v>190.6906906906907</v>
@@ -4119,7 +4130,7 @@
         <v>264.70741097059869</v>
       </c>
       <c r="U44">
-        <v>43</v>
+        <v>430</v>
       </c>
       <c r="V44">
         <v>178.37837837837839</v>
@@ -4202,7 +4213,7 @@
         <v>406.43909184616609</v>
       </c>
       <c r="U45">
-        <v>57</v>
+        <v>570</v>
       </c>
       <c r="V45">
         <v>157.65765765765767</v>
@@ -4285,7 +4296,7 @@
         <v>557.80870525368266</v>
       </c>
       <c r="U46">
-        <v>85</v>
+        <v>850</v>
       </c>
       <c r="V46">
         <v>138.43843843843842</v>
@@ -4368,7 +4379,7 @@
         <v>713.94888605603933</v>
       </c>
       <c r="U47">
-        <v>93</v>
+        <v>930</v>
       </c>
       <c r="V47">
         <v>121.62162162162163</v>
@@ -4451,7 +4462,7 @@
         <v>871.56368912785729</v>
       </c>
       <c r="U48">
-        <v>109</v>
+        <v>1090</v>
       </c>
       <c r="V48">
         <v>107.50750750750751</v>
@@ -4534,7 +4545,7 @@
         <v>1029.0964339001798</v>
       </c>
       <c r="U49">
-        <v>129</v>
+        <v>1290</v>
       </c>
       <c r="V49">
         <v>96.09609609609609</v>
@@ -4617,7 +4628,7 @@
         <v>1185.3007677572375</v>
       </c>
       <c r="U50">
-        <v>141</v>
+        <v>1410</v>
       </c>
       <c r="V50">
         <v>86.486486486486484</v>
@@ -4639,7 +4650,7 @@
       </c>
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="1" t="s">
         <v>35</v>
       </c>
     </row>
